--- a/tests/SafeOpenXml.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6088cd575f1b44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06116e286143440c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4960b0898c8c4e69"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd00d33690f4e4251"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R94bcb960a3ea4c32"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4bbc569178e64234"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f7ba4e2e1c426f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf7008e73cc44ec8"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06116e286143440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53ab894cc2f842cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd00d33690f4e4251"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raf54b3fe526b4a22"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4bbc569178e64234"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R763c1e7c108543c6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf7008e73cc44ec8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85db9379d2fc496d"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartAndImage/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartAndImage/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53ab894cc2f842cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f980e2a34404902"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raf54b3fe526b4a22"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3dc7942a124b4d64"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -165,7 +165,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R763c1e7c108543c6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R92735f920e064f41"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -213,6 +213,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85db9379d2fc496d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fda3fdf9a204880"/>
 </x:worksheet>
 </file>